--- a/daily_matches/job_matches_2026-06-29.xlsx
+++ b/daily_matches/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,175 +468,140 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr AI/ML Solutions Architect - PostgreSQL</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Apache Airflow, Databricks, Kafka, PostgreSQL, MySQL</t>
+          <t>RAG, S3, Redshift, Docker, Kubernetes, CI/CD, Git, Databricks, Redshift, NoSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e876a85ca956607c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Backend Platform Engineer (Python)</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Duo Health</t>
+          <t>bet365</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=964113b39e7ac1d1</t>
+          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer I</t>
+          <t>Founding Senior Software Engineer (USA + LATAM)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>RBC</t>
+          <t>Clipbook</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, Hugging Face, TensorFlow, PyTorch, Kubernetes, Git, Python, R</t>
+          <t>RAG, BigQuery, Docker, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8d4133e39033e3</t>
+          <t>https://www.indeed.com/viewjob?jk=68db649986ec9037</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer, Airflow</t>
+          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Tech Scalerz</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Philadelphia, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Docker, Kubernetes, Apache Airflow, Snowflake, Databricks, Redshift, PostgreSQL, Python</t>
+          <t>Data Scientist, Kubernetes, AKS, CI/CD, Databricks, PySpark, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a297ffaf533cd380</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Aftermarket Insights Sales Data Scientist</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Peoria, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, EC2, Apache Airflow, Git, Power BI, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-28</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88ec3a28e10d907a</t>
+          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-29.xlsx
+++ b/daily_matches/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Docker, Kubernetes, CI/CD, Git, Databricks, Redshift, NoSQL</t>
+          <t>Data Scientist, RAG, Redshift, Git, Redshift, PySpark, Kafka, Hadoop, Dask, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f0f3ea5b712aaf6</t>
+          <t>https://www.indeed.com/viewjob?jk=f82a5c6efb86f336</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Machine Learning Engineer (10187)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bet365</t>
+          <t>Extreme Networks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, GCP Vertex AI, Docker, Kubernetes, CI/CD, Terraform, Kafka, Python</t>
+          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=408ab6603d114356</t>
+          <t>https://www.indeed.com/viewjob?jk=aec9ca3f96869534</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Founding Senior Software Engineer (USA + LATAM)</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Clipbook</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,11 +552,11 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Docker, CI/CD, BigQuery, Kafka, PostgreSQL, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Cassandra, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,392 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68db649986ec9037</t>
+          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Azure Databricks, Spark, PySpark, Scala)</t>
+          <t>Infrastructure / DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tech Scalerz</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f36b86968d942b48</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>NLP Engineer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, NLP Engineer, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61c112ccf74884d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Intone Networks</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dunwoody, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, S3, Kinesis, CI/CD, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Member Experience Delivery (Open to hiring at the Software Engineer level)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Wellmark Blue Cross and Blue Shield</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, GitHub Actions, Git, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19a2938c48e268d6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>VINMAR INTERNATIONAL</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, FastAPI, Docker, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Data Analyst - 2373615</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S3, Athena, Apache Airflow, Snowflake, Tableau, Matplotlib, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84b219aef10b7fb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Brentwood, TN - 2373629</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Brentwood, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Data Scientist, Kubernetes, AKS, CI/CD, Databricks, PySpark, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-29</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5d65dc21087a459</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dc0aed0ba9d06eef</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Innovation Analyst</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Roofing Corp of America</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfe8df6f2d46ed2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Software Engineer II - Infrastructure</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Copilot, Docker, AKS, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6443c8a4d597a758</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docker, Git, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Sr. Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=803d2792ddeec470</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-29.xlsx
+++ b/daily_matches/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Software Engineer: Full-Stack Web Developer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Nanobiosym</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, Git, Redshift, PySpark, Kafka, Hadoop, Dask, Tableau</t>
+          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Tableau</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f82a5c6efb86f336</t>
+          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (10187)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Extreme Networks</t>
+          <t>Peloton</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, RAG, PyTorch, FastAPI, Docker, Kubernetes, CI/CD, Git, NoSQL</t>
+          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec9ca3f96869534</t>
+          <t>https://www.indeed.com/viewjob?jk=c978427a3579bc32</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MySQL, Cassandra, Python, SQL</t>
+          <t>Data Scientist, LangChain, RAG, Gemini, XGBoost, LightGBM, MLflow, CI/CD, Snowflake, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33da34be38b547b0</t>
+          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Infrastructure / DevOps Engineer</t>
+          <t>AI Software Engineer II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,15 +583,15 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36b86968d942b48</t>
+          <t>https://www.indeed.com/viewjob?jk=e59d582864de28bb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NLP Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ZENO Group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, NLP Engineer, Copilot, CI/CD, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Redshift, BigQuery, AKS, Snowflake, BigQuery, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61c112ccf74884d1</t>
+          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>PBK Architects</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dunwoody, GA, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, S3, Kinesis, CI/CD, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc7e459625948137</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Member Experience Delivery (Open to hiring at the Software Engineer level)</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wellmark Blue Cross and Blue Shield</t>
+          <t>The DarkStar Group</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Git, MongoDB, SQL, R, Java, Scala, Optimization</t>
+          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19a2938c48e268d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fefcbc3afed9caa2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Machine Learning Engineer - Computer Vision</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VINMAR INTERNATIONAL</t>
+          <t>Finalcover LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Terraform, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81e20cb883b5bbbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7f00adc42c4ef9bb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Analyst - 2373615</t>
+          <t>Data Engineer/Architect - MS Fabric</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, Athena, Apache Airflow, Snowflake, Tableau, Matplotlib, Python, SQL, R, Scala</t>
+          <t>RAG, Dataflow, CI/CD, PySpark, Hadoop, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84b219aef10b7fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Brentwood, TN - 2373629</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc0aed0ba9d06eef</t>
+          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Innovation Analyst</t>
+          <t>Software Engineer Full Stack Python</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Roofing Corp of America</t>
+          <t>ClinDCast LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Git, R, Scala</t>
+          <t>LangChain, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe8df6f2d46ed2c</t>
+          <t>https://www.indeed.com/viewjob?jk=108ebf9a9e4d3b0a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer II - Infrastructure</t>
+          <t>Software Engineer Developer Productivity &amp; Infrastructure, Autonomy</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, Docker, AKS, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6443c8a4d597a758</t>
+          <t>https://www.indeed.com/viewjob?jk=29b5921105e4a665</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Austin, TX - 2373630</t>
+          <t>LoopNet - Senior Software Engineer (C#/.NET)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Git, Kafka, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, Git, Kafka, MySQL, NoSQL, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ecbcebb77acdc85</t>
+          <t>https://www.indeed.com/viewjob?jk=5726e7c34b52ebf4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, PostgreSQL, Python, SQL, R, Java</t>
+          <t>CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,182 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=803d2792ddeec470</t>
+          <t>https://www.indeed.com/viewjob?jk=d57566bba0a6ced1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Sr Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Speria</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8719e11ff2abb97b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data and AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>JELLYFISH</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Full Stack Developer III</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PBK Architects</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Berkeley, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=665e40c6baa0ef61</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Pearson</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ebad94401f309a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst - Eden Prairie, MN - 2373646</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5f697e94d2ddae</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-29.xlsx
+++ b/daily_matches/job_matches_2026-06-29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer: Full-Stack Web Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nanobiosym</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Tableau</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Keras, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bf49a9803268a39</t>
+          <t>https://www.indeed.com/viewjob?jk=0d49a70c4f87ce0f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Cloud Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Peloton</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL, MySQL, Cassandra, NoSQL</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c978427a3579bc32</t>
+          <t>https://www.indeed.com/viewjob?jk=ef4c425e913ad44b</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Team Velocity Marketing</t>
+          <t>Cushman &amp; Wakefield</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Creve Coeur, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Gemini, XGBoost, LightGBM, MLflow, CI/CD, Snowflake, Python</t>
+          <t>Prompt Engineering, Data Lake, MLflow, FastAPI, Kubernetes, AKS, CI/CD, Terraform, Databricks, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7e753d624ac7894</t>
+          <t>https://www.indeed.com/viewjob?jk=3fed8aee2bab65bb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Software Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ndustrial.io</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL</t>
+          <t>AI Engineer, RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e59d582864de28bb</t>
+          <t>https://www.indeed.com/viewjob?jk=59bc7a106dfa1515</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, DevOps</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ZENO Group</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, BigQuery, AKS, Snowflake, BigQuery, Redshift, Tableau, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MySQL, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf46770fd8ff6a55</t>
+          <t>https://www.indeed.com/viewjob?jk=d3933dfeda45c057</t>
         </is>
       </c>
     </row>
@@ -648,20 +648,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Green Mountain Power</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Colchester, VT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, Snowflake, Databricks, Kafka, PostgreSQL, Power BI, Python, SQL</t>
+          <t>S3, Apache Airflow, Git, Snowflake, Hadoop, PostgreSQL, MongoDB, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea10b210ba9e582</t>
+          <t>https://www.indeed.com/viewjob?jk=3d9f58a4baa94d06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UX Software Engineer</t>
+          <t>Salesforce Developer (Hybrid/Columbia MD or Boston MA)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The DarkStar Group</t>
+          <t>Tenable</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
+          <t>RAG, Copilot, Data Lake, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fefcbc3afed9caa2</t>
+          <t>https://www.indeed.com/viewjob?jk=2103938d18681ae1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Computer Vision</t>
+          <t>AI-ML Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Finalcover LLC</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, Git, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, NoSQL, Matplotlib, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f00adc42c4ef9bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d6f5001cf103caa1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer/Architect - MS Fabric</t>
+          <t>Senior Fullstack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Dataflow, CI/CD, PySpark, Hadoop, Tableau, Power BI, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baea501e7691a719</t>
+          <t>https://www.indeed.com/viewjob?jk=dcc975e3071a9e35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Fullstack Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95668eacef5ebd13</t>
+          <t>https://www.indeed.com/viewjob?jk=3b8b1a71db432bac</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack Python</t>
+          <t>Senior Fullstack Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ClinDCast LLC</t>
+          <t>_coderio</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=108ebf9a9e4d3b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=d764f940fd823a00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer Developer Productivity &amp; Infrastructure, Autonomy</t>
+          <t>Database Engineer (contract)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>RAG, CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29b5921105e4a665</t>
+          <t>https://www.indeed.com/viewjob?jk=7bbb3ea9ee7ee707</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer (C#/.NET)</t>
+          <t>Software Engineer, Sr.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Harris Computer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Kafka, MySQL, NoSQL, SQL, R, Optimization</t>
+          <t>Copilot, Prompt Engineering, Git, PostgreSQL, MySQL, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5726e7c34b52ebf4</t>
+          <t>https://www.indeed.com/viewjob?jk=7ea652c383f00058</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bozeman, MT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CI/CD, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57566bba0a6ced1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d2413f123744bc5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Devops Engineer</t>
+          <t>Associate Actuary</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Speria</t>
+          <t>Wildfire Defense Systems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8719e11ff2abb97b</t>
+          <t>https://www.indeed.com/viewjob?jk=45e40dedeb41804c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data and AI Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JELLYFISH</t>
+          <t>Koch</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Wichita, KS, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Terraform, Databricks, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Copilot, S3, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6845c8c42d45017a</t>
+          <t>https://www.indeed.com/viewjob?jk=533b7936f244d6a6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer III</t>
+          <t>AI DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PBK Architects</t>
+          <t>Atkore</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Mokena, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+          <t>Azure ML, Azure ML Studio, Data Lake, Docker, Kubernetes, CI/CD, Terraform, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=665e40c6baa0ef61</t>
+          <t>https://www.indeed.com/viewjob?jk=ec1b6107c8004710</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pearson</t>
+          <t>Jewelers Mutual Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Optimization</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebad94401f309a3</t>
+          <t>https://www.indeed.com/viewjob?jk=175c183e086569b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Analyst - Eden Prairie, MN - 2373646</t>
+          <t>Software Engineer, Global Banking Loans</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>UBS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Weehawken, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Jenkins, Git, Kafka, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,112 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa5f697e94d2ddae</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ded20067faa3bf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Minnetonka, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c30d6a080ba3a942</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Analyst, Data Science</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LPL Financial</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Git, Snowflake, Python, SQL, R, Scala, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09b1f4b58f5d83ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist II- Data Algorithms &amp; Optimization, Cat Digital</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Python, R, Scala, Optimization, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c5b8b9b2889f309e</t>
         </is>
       </c>
     </row>
